--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2021_aysen.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">O'Higgins</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:21</t>
+    <t xml:space="preserve">2026-09-10 00:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -638,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11102</v>
+        <v>11302</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -651,7 +651,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11302</v>
+        <v>11102</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:27</t>
+    <t xml:space="preserve">2026-09-18 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
